--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488213_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488213_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.3906</v>
+        <v>13.2533</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9284</v>
+        <v>8.1357</v>
       </c>
       <c r="F2" t="n">
-        <v>5.4623</v>
+        <v>5.1176</v>
       </c>
       <c r="G2" t="n">
         <v>10.6612</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2139</v>
+        <v>1.0766</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1567</v>
+        <v>0.3641</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0572</v>
+        <v>0.7125</v>
       </c>
       <c r="V2" t="n">
         <v>5.036</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5573</v>
+        <v>7.8676</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6891</v>
+        <v>6.7778</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8682</v>
+        <v>1.0898</v>
       </c>
       <c r="G3" t="n">
         <v>6.6357</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6904</v>
+        <v>0.6199</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2226</v>
+        <v>0.8661</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4678</v>
+        <v>-0.2462</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9686</v>
+        <v>5.0064</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9686</v>
+        <v>1.6863</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>3.3201</v>
       </c>
       <c r="G4" t="n">
         <v>4.713</v>
@@ -766,13 +766,13 @@
         <v>2.2234</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8115</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0831</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2716</v>
+        <v>0.0485</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6054</v>
+        <v>3.6771</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6278</v>
+        <v>-0.2361</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2332</v>
+        <v>3.9131</v>
       </c>
       <c r="G5" t="n">
         <v>2.3945</v>
@@ -844,13 +844,13 @@
         <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9145</v>
+        <v>0.9861</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0037</v>
+        <v>0.388</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9182</v>
+        <v>0.5981</v>
       </c>
       <c r="V5" t="n">
         <v>-0.63</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0343</v>
+        <v>1.8494</v>
       </c>
       <c r="E6" t="n">
-        <v>1.682</v>
+        <v>1.5956</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3523</v>
+        <v>0.2538</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2793</v>
@@ -922,13 +922,13 @@
         <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0374</v>
+        <v>0.8524</v>
       </c>
       <c r="T6" t="n">
-        <v>1.302</v>
+        <v>1.2156</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2647</v>
+        <v>-0.3631</v>
       </c>
       <c r="V6" t="n">
         <v>2.8321</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>C. ÁLVAREZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4509</v>
+        <v>0.3221</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0773</v>
+        <v>0.3221</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5282</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0354</v>
+        <v>0.3221</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7589</v>
+        <v>0.3221</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7235</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1692</v>
+        <v>0.3221</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2628</v>
+        <v>0.3221</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0936</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1337</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4961</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6299</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4308</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7039</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2731</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. ÁLVAREZ GONZÁLEZ</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3221</v>
+        <v>0.1812</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3221</v>
+        <v>-1.2732</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.4544</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3221</v>
+        <v>-1.0354</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3221</v>
+        <v>-1.7589</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.7235</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3221</v>
+        <v>-1.1692</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3221</v>
+        <v>-1.2628</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0936</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.1337</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.4961</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.6299</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.508</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0.347</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.24</v>
+        <v>-0.2892</v>
       </c>
       <c r="E10" t="n">
         <v>0.5058</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7458</v>
+        <v>-0.795</v>
       </c>
       <c r="G10" t="n">
         <v>1.1088</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5019</v>
+        <v>0.4526</v>
       </c>
       <c r="T10" t="n">
         <v>0.485</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0169</v>
+        <v>-0.0324</v>
       </c>
       <c r="V10" t="n">
         <v>-3.1477</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. ANDRADE</t>
+          <t>J. MALPICA PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7966</v>
+        <v>-1.1548</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8281</v>
+        <v>-1.6373</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0315</v>
+        <v>0.4825</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5076</v>
+        <v>0.2399</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2111</v>
+        <v>0.4596</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2965</v>
+        <v>-0.2197</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6207</v>
+        <v>-0.5899</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8079</v>
+        <v>0.0215</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8128</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.887</v>
+        <v>0.8299</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4033</v>
+        <v>0.4381</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4837</v>
+        <v>0.3917</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0382</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1361</v>
+        <v>-0.1359</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5719</v>
+        <v>-0.1209</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4358</v>
+        <v>-0.0149</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5749</v>
+        <v>-1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3161</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3933</v>
+        <v>-1.2462</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8096</v>
+        <v>-1.7117</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4163</v>
+        <v>0.4655</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3714</v>
@@ -1390,13 +1390,13 @@
         <v>0.3706</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2072</v>
+        <v>-0.06</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.383</v>
+        <v>-0.2851</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1758</v>
+        <v>0.2251</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MALPICA PEREZ</t>
+          <t>E. ANDRADE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4004</v>
+        <v>-1.5926</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7352</v>
+        <v>-2.698</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3348</v>
+        <v>1.1054</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2399</v>
+        <v>-3.5076</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4596</v>
+        <v>-1.2111</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2197</v>
+        <v>-2.2965</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5899</v>
+        <v>-2.6207</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0215</v>
+        <v>-0.8079</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-1.8128</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8299</v>
+        <v>-0.887</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4381</v>
+        <v>-0.4033</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3917</v>
+        <v>-0.4837</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9264</v>
+        <v>-2.0382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9264</v>
+        <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3815</v>
+        <v>0.3401</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2189</v>
+        <v>0.702</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1627</v>
+        <v>-0.3619</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2589</v>
+        <v>1.5749</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2589</v>
+        <v>0.3161</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.3975</v>
+        <v>-2.2257</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.736</v>
+        <v>-2.6381</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3385</v>
+        <v>0.4124</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0197</v>
@@ -1546,13 +1546,13 @@
         <v>0.7411</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4519</v>
+        <v>-0.2801</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3425</v>
+        <v>-0.2686</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6289</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>25.74549999999999</v>
+        <v>26.2927</v>
       </c>
       <c r="E15" t="n">
-        <v>8.9261</v>
+        <v>9.472999999999997</v>
       </c>
       <c r="F15" t="n">
-        <v>16.8195</v>
+        <v>16.8196</v>
       </c>
       <c r="G15" t="n">
         <v>19.5059</v>
@@ -1594,7 +1594,7 @@
         <v>14.1308</v>
       </c>
       <c r="I15" t="n">
-        <v>5.374999999999998</v>
+        <v>5.375</v>
       </c>
       <c r="J15" t="n">
         <v>16.134</v>
@@ -1612,7 +1612,7 @@
         <v>2.6409</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7309000000000001</v>
+        <v>0.7309</v>
       </c>
       <c r="P15" t="n">
         <v>-1.8531</v>
@@ -1624,16 +1624,16 @@
         <v>18.5287</v>
       </c>
       <c r="S15" t="n">
-        <v>4.315099999999999</v>
+        <v>4.862</v>
       </c>
       <c r="T15" t="n">
-        <v>4.365</v>
+        <v>4.9122</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.05010000000000009</v>
+        <v>-0.0499</v>
       </c>
       <c r="V15" t="n">
-        <v>3.777499999999999</v>
+        <v>3.7775</v>
       </c>
       <c r="W15" t="n">
         <v>8.808700000000002</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>D. POL RUBIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2681</v>
+        <v>1.3092</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0611</v>
+        <v>-0.346</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.793</v>
+        <v>1.6552</v>
       </c>
       <c r="G16" t="n">
-        <v>0.064</v>
+        <v>0.5263</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7594</v>
+        <v>0.0824</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6954</v>
+        <v>0.4439</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3317</v>
+        <v>-0.2659</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2073</v>
+        <v>0.3348</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1244</v>
+        <v>-0.6007</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2677</v>
+        <v>0.7922</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4478</v>
+        <v>-0.2524</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8198</v>
+        <v>1.0446</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.594</v>
+        <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>1.155</v>
+        <v>-0.4579</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5829</v>
+        <v>-0.3945</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4278</v>
+        <v>-0.0634</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6921</v>
+        <v>0.3144</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0005</v>
+        <v>0.3144</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. POL RUBIO</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0143</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4439</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4582</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5263</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0824</v>
+        <v>0.3221</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4439</v>
+        <v>0.6221</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2659</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3348</v>
+        <v>0.3221</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6007</v>
+        <v>0.6221</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7922</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2524</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0446</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7528</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4924</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2604</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>P. CORREA GALLARDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.5283</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.6217</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.3932</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3221</v>
+        <v>0.152</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6221</v>
+        <v>-0.5453</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9441000000000001</v>
+        <v>-0.6314</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3221</v>
+        <v>0.0215</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6221</v>
+        <v>-0.6529</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.2381</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.1306</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.1076</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.0075</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3777</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3777</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7285</v>
+        <v>0.2125</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0168</v>
+        <v>1.8209</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2883</v>
+        <v>-1.6084</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6287</v>
@@ -1936,13 +1936,13 @@
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4957</v>
+        <v>-1.0116</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0199</v>
+        <v>-0.2157</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4758</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0.6294</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CORREA GALLARDO</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3565</v>
+        <v>0.1187</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7197</v>
+        <v>2.6901</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0762</v>
+        <v>-2.5714</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3932</v>
+        <v>0.064</v>
       </c>
       <c r="H20" t="n">
-        <v>0.152</v>
+        <v>1.7594</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5453</v>
+        <v>-1.6954</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6314</v>
+        <v>3.3317</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0215</v>
+        <v>3.2073</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6529</v>
+        <v>0.1244</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2381</v>
+        <v>-3.2677</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1306</v>
+        <v>-1.4478</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1076</v>
+        <v>-1.8198</v>
       </c>
       <c r="P20" t="n">
-        <v>1.297</v>
+        <v>0.7411</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>1.297</v>
+        <v>2.594</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1696</v>
+        <v>0.0056</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0883</v>
+        <v>1.2119</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0813</v>
+        <v>-1.2063</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3777</v>
+        <v>-0.6921</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3777</v>
+        <v>-0.6915</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1327</v>
+        <v>0.0883</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8088</v>
+        <v>-0.7108</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6761</v>
+        <v>0.7992</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2359</v>
@@ -2092,13 +2092,13 @@
         <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2674</v>
+        <v>-0.0463</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2268</v>
+        <v>-1.7858</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4153</v>
+        <v>-1.0236</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8115</v>
+        <v>-0.7623</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2525</v>
@@ -2170,13 +2170,13 @@
         <v>2.0382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7083</v>
+        <v>-0.2674</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2313</v>
+        <v>0.1604</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.477</v>
+        <v>-0.4278</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3777</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6195</v>
+        <v>-2.202</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1461</v>
+        <v>-1.9502</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4734</v>
+        <v>-0.2518</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9786</v>
@@ -2248,13 +2248,13 @@
         <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3259</v>
+        <v>-0.9084</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6901</v>
+        <v>-0.4943</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6357</v>
+        <v>-0.4141</v>
       </c>
       <c r="V23" t="n">
         <v>0.3144</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1629</v>
+        <v>-3.1892</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2911</v>
+        <v>-3.9974</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1282</v>
+        <v>0.8082</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5702</v>
@@ -2326,13 +2326,13 @@
         <v>1.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2221</v>
+        <v>-0.2484</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9849</v>
+        <v>-0.6911</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7628</v>
+        <v>0.4427</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4347</v>
+        <v>-3.5081</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6403</v>
+        <v>-3.7382</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2055</v>
+        <v>0.2302</v>
       </c>
       <c r="G25" t="n">
         <v>-3.232</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0376</v>
+        <v>-0.0358</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2027</v>
+        <v>0.1048</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1652</v>
+        <v>-0.1405</v>
       </c>
       <c r="V25" t="n">
         <v>0.3155</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.8801</v>
+        <v>-4.222</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7348</v>
+        <v>-3.2245</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1453</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-2.9485</v>
@@ -2482,13 +2482,13 @@
         <v>2.7793</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0401</v>
+        <v>-0.3019</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.4928</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9424</v>
+        <v>-0.7946</v>
       </c>
       <c r="V26" t="n">
         <v>0.8812</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.3989</v>
+        <v>-4.8365</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.2371</v>
+        <v>-1.5516</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.1618</v>
+        <v>-3.2849</v>
       </c>
       <c r="G27" t="n">
         <v>-3.678</v>
@@ -2560,13 +2560,13 @@
         <v>2.0382</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.8991</v>
+        <v>-0.3367</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.1476</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0659</v>
+        <v>-0.189</v>
       </c>
       <c r="V27" t="n">
         <v>-1.0071</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-9.2014</v>
+        <v>-9.203099999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.4045</v>
+        <v>-5.1107</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.7969</v>
+        <v>-4.0924</v>
       </c>
       <c r="G28" t="n">
         <v>-4.1223</v>
@@ -2638,13 +2638,13 @@
         <v>1.8529</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.7068</v>
+        <v>-0.7085</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1591</v>
+        <v>0.1346</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.5477</v>
+        <v>-0.8431</v>
       </c>
       <c r="V28" t="n">
         <v>-2.5194</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-25.7455</v>
+        <v>-25.7456</v>
       </c>
       <c r="E29" t="n">
         <v>-16.8196</v>
       </c>
       <c r="F29" t="n">
-        <v>-8.925999999999998</v>
+        <v>-8.9259</v>
       </c>
       <c r="G29" t="n">
         <v>-19.5055</v>
@@ -2689,13 +2689,13 @@
         <v>-5.3748</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.371799999999999</v>
+        <v>-3.3718</v>
       </c>
       <c r="K29" t="n">
         <v>-2.6408</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.7308000000000002</v>
+        <v>-0.7308</v>
       </c>
       <c r="M29" t="n">
         <v>-16.134</v>
@@ -2716,10 +2716,10 @@
         <v>20.3816</v>
       </c>
       <c r="S29" t="n">
-        <v>-4.315000000000001</v>
+        <v>-4.3151</v>
       </c>
       <c r="T29" t="n">
-        <v>0.04990000000000019</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="U29" t="n">
         <v>-4.3649</v>
